--- a/AAII_Financials/Yearly/SRAD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SRAD_YR_FIN.xlsx
@@ -766,13 +766,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1116300</v>
+        <v>1108400</v>
       </c>
       <c r="E9" s="3">
-        <v>856900</v>
+        <v>855200</v>
       </c>
       <c r="F9" s="3">
-        <v>733500</v>
+        <v>724700</v>
       </c>
       <c r="G9" s="3">
         <v>603200</v>
@@ -808,13 +808,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>398300</v>
+        <v>406200</v>
       </c>
       <c r="E10" s="3">
-        <v>288700</v>
+        <v>290400</v>
       </c>
       <c r="F10" s="3">
-        <v>236500</v>
+        <v>245400</v>
       </c>
       <c r="G10" s="3">
         <v>177100</v>
@@ -952,13 +952,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1100</v>
+        <v>66400</v>
       </c>
       <c r="E14" s="3">
-        <v>200</v>
+        <v>5400</v>
       </c>
       <c r="F14" s="3">
-        <v>25900</v>
+        <v>34800</v>
       </c>
       <c r="G14" s="3">
         <v>-8200</v>
@@ -1051,13 +1051,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1377300</v>
+        <v>1312000</v>
       </c>
       <c r="E17" s="3">
-        <v>1012200</v>
+        <v>1007000</v>
       </c>
       <c r="F17" s="3">
-        <v>890400</v>
+        <v>881600</v>
       </c>
       <c r="G17" s="3">
         <v>755100</v>
@@ -1093,13 +1093,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>137200</v>
+        <v>202600</v>
       </c>
       <c r="E18" s="3">
-        <v>133400</v>
+        <v>138600</v>
       </c>
       <c r="F18" s="3">
-        <v>79600</v>
+        <v>88500</v>
       </c>
       <c r="G18" s="3">
         <v>25300</v>
@@ -1195,13 +1195,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>309100</v>
+        <v>374500</v>
       </c>
       <c r="E21" s="3">
-        <v>146700</v>
+        <v>151900</v>
       </c>
       <c r="F21" s="3">
-        <v>155600</v>
+        <v>164400</v>
       </c>
       <c r="G21" s="3">
         <v>95600</v>
